--- a/data/direct/wordstat_2026-10-28.xlsx
+++ b/data/direct/wordstat_2026-10-28.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F193"/>
+  <dimension ref="A1:F194"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -4997,46 +4997,62 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="6" t="inlineStr">
+      <c r="A172" s="3" t="inlineStr">
         <is>
           <t>ошибка 01315</t>
         </is>
       </c>
-      <c r="B172" s="6" t="n">
+      <c r="B172" s="3" t="n">
         <v>309</v>
       </c>
-      <c r="C172" s="6" t="inlineStr">
-        <is>
-          <t>не брать</t>
-        </is>
-      </c>
-      <c r="D172" s="6" t="inlineStr"/>
-      <c r="E172" s="6" t="inlineStr"/>
-      <c r="F172" s="6" t="inlineStr">
-        <is>
-          <t>голый 01315 — по правилу не берём</t>
+      <c r="C172" s="3" t="inlineStr">
+        <is>
+          <t>под вопросом</t>
+        </is>
+      </c>
+      <c r="D172" s="3" t="inlineStr">
+        <is>
+          <t>dq200_errors.tsv</t>
+        </is>
+      </c>
+      <c r="E172" s="3" t="inlineStr">
+        <is>
+          <t>? 01315 связь с блоком коробки</t>
+        </is>
+      </c>
+      <c r="F172" s="3" t="inlineStr">
+        <is>
+          <t>расширения 01315 в Вордстате — только VAG (проверено 28.10); Audi A4/A6/A8/Q — минус-словами группы</t>
         </is>
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="6" t="inlineStr">
+      <c r="A173" s="3" t="inlineStr">
         <is>
           <t>01315 ошибка ауди</t>
         </is>
       </c>
-      <c r="B173" s="6" t="n">
+      <c r="B173" s="3" t="n">
         <v>72</v>
       </c>
-      <c r="C173" s="6" t="inlineStr">
-        <is>
-          <t>не брать</t>
-        </is>
-      </c>
-      <c r="D173" s="6" t="inlineStr"/>
-      <c r="E173" s="6" t="inlineStr"/>
-      <c r="F173" s="6" t="inlineStr">
-        <is>
-          <t>часто вариатор</t>
+      <c r="C173" s="3" t="inlineStr">
+        <is>
+          <t>под вопросом</t>
+        </is>
+      </c>
+      <c r="D173" s="3" t="inlineStr">
+        <is>
+          <t>dq200_errors.tsv</t>
+        </is>
+      </c>
+      <c r="E173" s="3" t="inlineStr">
+        <is>
+          <t>? 01315 связь с блоком коробки</t>
+        </is>
+      </c>
+      <c r="F173" s="3" t="inlineStr">
+        <is>
+          <t>расширения 01315 в Вордстате — только VAG (проверено 28.10); Audi A4/A6/A8/Q — минус-словами группы</t>
         </is>
       </c>
     </row>
@@ -5477,6 +5493,36 @@
       <c r="F193" s="6" t="inlineStr">
         <is>
           <t>Passat B5 — без DSG</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="3" t="inlineStr">
+        <is>
+          <t>01315</t>
+        </is>
+      </c>
+      <c r="B194" s="3" t="n">
+        <v>543</v>
+      </c>
+      <c r="C194" s="3" t="inlineStr">
+        <is>
+          <t>под вопросом</t>
+        </is>
+      </c>
+      <c r="D194" s="3" t="inlineStr">
+        <is>
+          <t>dq200_errors.tsv</t>
+        </is>
+      </c>
+      <c r="E194" s="3" t="inlineStr">
+        <is>
+          <t>? 01315 связь с блоком коробки</t>
+        </is>
+      </c>
+      <c r="F194" s="3" t="inlineStr">
+        <is>
+          <t>голый код: все расширения VAG; мусор «пб68», «18790» — минус-словами</t>
         </is>
       </c>
     </row>

--- a/data/direct/wordstat_2026-10-28.xlsx
+++ b/data/direct/wordstat_2026-10-28.xlsx
@@ -3117,90 +3117,122 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="4" t="inlineStr">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>p189c</t>
         </is>
       </c>
-      <c r="B98" s="4" t="n">
+      <c r="B98" s="2" t="n">
         <v>225</v>
       </c>
-      <c r="C98" s="4" t="inlineStr">
-        <is>
-          <t>проверить</t>
-        </is>
-      </c>
-      <c r="D98" s="4" t="inlineStr"/>
-      <c r="E98" s="4" t="inlineStr"/>
-      <c r="F98" s="4" t="inlineStr">
-        <is>
-          <t>голый код — по правилу сначала расширения в Вордстате (нет ли чужих марок)</t>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>взять</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>dq200_errors.tsv</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>P189C</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>голый код: расширения проверены 28.10 — чужих марок нет</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="4" t="inlineStr">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>ошибка p189c</t>
         </is>
       </c>
-      <c r="B99" s="4" t="n">
+      <c r="B99" s="2" t="n">
         <v>153</v>
       </c>
-      <c r="C99" s="4" t="inlineStr">
-        <is>
-          <t>проверить</t>
-        </is>
-      </c>
-      <c r="D99" s="4" t="inlineStr"/>
-      <c r="E99" s="4" t="inlineStr"/>
-      <c r="F99" s="4" t="inlineStr">
-        <is>
-          <t>голый код — по правилу сначала расширения в Вордстате (нет ли чужих марок)</t>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>взять</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>dq200_errors.tsv</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>P189C</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>расширения проверены 28.10 — чужих марок нет</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="4" t="inlineStr">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>0am325025d</t>
         </is>
       </c>
-      <c r="B100" s="4" t="n">
+      <c r="B100" s="2" t="n">
         <v>82</v>
       </c>
-      <c r="C100" s="4" t="inlineStr">
-        <is>
-          <t>проверить</t>
-        </is>
-      </c>
-      <c r="D100" s="4" t="inlineStr"/>
-      <c r="E100" s="4" t="inlineStr"/>
-      <c r="F100" s="4" t="inlineStr">
-        <is>
-          <t>ищут реальный каталожный номер VAG? У нас D/L/M — внутренние коды, не мехатроник</t>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>взять</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>dq200_landing.tsv</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 общий</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>решение владельца 28.10</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="4" t="inlineStr">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>p189c00</t>
         </is>
       </c>
-      <c r="B101" s="4" t="n">
+      <c r="B101" s="2" t="n">
         <v>69</v>
       </c>
-      <c r="C101" s="4" t="inlineStr">
-        <is>
-          <t>проверить</t>
-        </is>
-      </c>
-      <c r="D101" s="4" t="inlineStr"/>
-      <c r="E101" s="4" t="inlineStr"/>
-      <c r="F101" s="4" t="inlineStr">
-        <is>
-          <t>голый код — по правилу сначала расширения в Вордстате (нет ли чужих марок)</t>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>взять</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>dq200_errors.tsv</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>P189C</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>расширения проверены 28.10 — чужих марок нет</t>
         </is>
       </c>
     </row>
@@ -3227,24 +3259,24 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="4" t="inlineStr">
+      <c r="A103" s="6" t="inlineStr">
         <is>
           <t>0am325025m</t>
         </is>
       </c>
-      <c r="B103" s="4" t="n">
+      <c r="B103" s="6" t="n">
         <v>26</v>
       </c>
-      <c r="C103" s="4" t="inlineStr">
-        <is>
-          <t>проверить</t>
-        </is>
-      </c>
-      <c r="D103" s="4" t="inlineStr"/>
-      <c r="E103" s="4" t="inlineStr"/>
-      <c r="F103" s="4" t="inlineStr">
-        <is>
-          <t>ищут реальный каталожный номер VAG? У нас D/L/M — внутренние коды, не мехатроник</t>
+      <c r="C103" s="6" t="inlineStr">
+        <is>
+          <t>не брать</t>
+        </is>
+      </c>
+      <c r="D103" s="6" t="inlineStr"/>
+      <c r="E103" s="6" t="inlineStr"/>
+      <c r="F103" s="6" t="inlineStr">
+        <is>
+          <t>владелец проверил 28.10: нет в Вордстате</t>
         </is>
       </c>
     </row>
@@ -3271,24 +3303,24 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="4" t="inlineStr">
+      <c r="A105" s="6" t="inlineStr">
         <is>
           <t>0am325025l</t>
         </is>
       </c>
-      <c r="B105" s="4" t="n">
+      <c r="B105" s="6" t="n">
         <v>15</v>
       </c>
-      <c r="C105" s="4" t="inlineStr">
-        <is>
-          <t>проверить</t>
-        </is>
-      </c>
-      <c r="D105" s="4" t="inlineStr"/>
-      <c r="E105" s="4" t="inlineStr"/>
-      <c r="F105" s="4" t="inlineStr">
-        <is>
-          <t>ищут реальный каталожный номер VAG? У нас D/L/M — внутренние коды, не мехатроник</t>
+      <c r="C105" s="6" t="inlineStr">
+        <is>
+          <t>не брать</t>
+        </is>
+      </c>
+      <c r="D105" s="6" t="inlineStr"/>
+      <c r="E105" s="6" t="inlineStr"/>
+      <c r="F105" s="6" t="inlineStr">
+        <is>
+          <t>владелец проверил 28.10: нет в Вордстате</t>
         </is>
       </c>
     </row>
@@ -3315,24 +3347,24 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="4" t="inlineStr">
+      <c r="A107" s="6" t="inlineStr">
         <is>
           <t>0am325025d ремкомплект</t>
         </is>
       </c>
-      <c r="B107" s="4" t="n">
+      <c r="B107" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="C107" s="4" t="inlineStr">
-        <is>
-          <t>проверить</t>
-        </is>
-      </c>
-      <c r="D107" s="4" t="inlineStr"/>
-      <c r="E107" s="4" t="inlineStr"/>
-      <c r="F107" s="4" t="inlineStr">
-        <is>
-          <t>ищут реальный каталожный номер VAG? У нас D/L/M — внутренние коды, не мехатроник</t>
+      <c r="C107" s="6" t="inlineStr">
+        <is>
+          <t>не брать</t>
+        </is>
+      </c>
+      <c r="D107" s="6" t="inlineStr"/>
+      <c r="E107" s="6" t="inlineStr"/>
+      <c r="F107" s="6" t="inlineStr">
+        <is>
+          <t>ремкомплект — минус-слово кампании, не товар посадочной</t>
         </is>
       </c>
     </row>
@@ -3359,24 +3391,24 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="4" t="inlineStr">
+      <c r="A109" s="6" t="inlineStr">
         <is>
           <t>0am325025l z1t</t>
         </is>
       </c>
-      <c r="B109" s="4" t="n">
+      <c r="B109" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="C109" s="4" t="inlineStr">
-        <is>
-          <t>проверить</t>
-        </is>
-      </c>
-      <c r="D109" s="4" t="inlineStr"/>
-      <c r="E109" s="4" t="inlineStr"/>
-      <c r="F109" s="4" t="inlineStr">
-        <is>
-          <t>ищут реальный каталожный номер VAG? У нас D/L/M — внутренние коды, не мехатроник</t>
+      <c r="C109" s="6" t="inlineStr">
+        <is>
+          <t>не брать</t>
+        </is>
+      </c>
+      <c r="D109" s="6" t="inlineStr"/>
+      <c r="E109" s="6" t="inlineStr"/>
+      <c r="F109" s="6" t="inlineStr">
+        <is>
+          <t>владелец проверил 28.10: нет в Вордстате</t>
         </is>
       </c>
     </row>

--- a/data/direct/wordstat_2026-10-28.xlsx
+++ b/data/direct/wordstat_2026-10-28.xlsx
@@ -3237,24 +3237,32 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="4" t="inlineStr">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>p173c ошибка dsg 7 dq200</t>
         </is>
       </c>
-      <c r="B102" s="4" t="n">
+      <c r="B102" s="2" t="n">
         <v>34</v>
       </c>
-      <c r="C102" s="4" t="inlineStr">
-        <is>
-          <t>проверить</t>
-        </is>
-      </c>
-      <c r="D102" s="4" t="inlineStr"/>
-      <c r="E102" s="4" t="inlineStr"/>
-      <c r="F102" s="4" t="inlineStr">
-        <is>
-          <t>код не подтверждён источниками как мехатроник DQ200 — не беру до проверки</t>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>взять</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>dq200_errors.tsv</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>P173C</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>проверено 28.10: датчик хода 3 переключателя передач, DQ200 (dsgservice-spb, drive2)</t>
         </is>
       </c>
     </row>

--- a/data/direct/wordstat_2026-10-28.xlsx
+++ b/data/direct/wordstat_2026-10-28.xlsx
@@ -2249,46 +2249,46 @@
       <c r="F65" s="2" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="3" t="inlineStr">
+      <c r="A66" s="6" t="inlineStr">
         <is>
           <t>ремонт платы dq200</t>
         </is>
       </c>
-      <c r="B66" s="3" t="n">
+      <c r="B66" s="6" t="n">
         <v>252</v>
       </c>
-      <c r="C66" s="3" t="inlineStr">
-        <is>
-          <t>под вопросом</t>
-        </is>
-      </c>
-      <c r="D66" s="3" t="inlineStr"/>
-      <c r="E66" s="3" t="inlineStr"/>
-      <c r="F66" s="3" t="inlineStr">
-        <is>
-          <t>ремонт/замена — минус-слова кампании; «замена платы» может быть покупкой — решить</t>
+      <c r="C66" s="6" t="inlineStr">
+        <is>
+          <t>не брать</t>
+        </is>
+      </c>
+      <c r="D66" s="6" t="inlineStr"/>
+      <c r="E66" s="6" t="inlineStr"/>
+      <c r="F66" s="6" t="inlineStr">
+        <is>
+          <t>ремонт — запрос на услугу, мы не ремонтируем</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="3" t="inlineStr">
+      <c r="A67" s="6" t="inlineStr">
         <is>
           <t>ремонт платы мехатроника dq200</t>
         </is>
       </c>
-      <c r="B67" s="3" t="n">
+      <c r="B67" s="6" t="n">
         <v>166</v>
       </c>
-      <c r="C67" s="3" t="inlineStr">
-        <is>
-          <t>под вопросом</t>
-        </is>
-      </c>
-      <c r="D67" s="3" t="inlineStr"/>
-      <c r="E67" s="3" t="inlineStr"/>
-      <c r="F67" s="3" t="inlineStr">
-        <is>
-          <t>ремонт/замена — минус-слова кампании; «замена платы» может быть покупкой — решить</t>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>не брать</t>
+        </is>
+      </c>
+      <c r="D67" s="6" t="inlineStr"/>
+      <c r="E67" s="6" t="inlineStr"/>
+      <c r="F67" s="6" t="inlineStr">
+        <is>
+          <t>ремонт — запрос на услугу, мы не ремонтируем</t>
         </is>
       </c>
     </row>
@@ -2306,11 +2306,19 @@
           <t>под вопросом</t>
         </is>
       </c>
-      <c r="D68" s="3" t="inlineStr"/>
-      <c r="E68" s="3" t="inlineStr"/>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>dq200_landing.tsv</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="inlineStr">
+        <is>
+          <t>? Замена платы DQ200</t>
+        </is>
+      </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>ремонт/замена — минус-слова кампании; «замена платы» может быть покупкой — решить</t>
+          <t>замена = покупка новой платы; ставка 40 ₽</t>
         </is>
       </c>
     </row>
@@ -2328,33 +2336,41 @@
           <t>под вопросом</t>
         </is>
       </c>
-      <c r="D69" s="3" t="inlineStr"/>
-      <c r="E69" s="3" t="inlineStr"/>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>dq200_landing.tsv</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="inlineStr">
+        <is>
+          <t>? Замена платы DQ200</t>
+        </is>
+      </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>ремонт/замена — минус-слова кампании; «замена платы» может быть покупкой — решить</t>
+          <t>замена = покупка новой платы; ставка 40 ₽</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="3" t="inlineStr">
+      <c r="A70" s="6" t="inlineStr">
         <is>
           <t>ремонт платы мехатроника dsg 7 dq200</t>
         </is>
       </c>
-      <c r="B70" s="3" t="n">
+      <c r="B70" s="6" t="n">
         <v>94</v>
       </c>
-      <c r="C70" s="3" t="inlineStr">
-        <is>
-          <t>под вопросом</t>
-        </is>
-      </c>
-      <c r="D70" s="3" t="inlineStr"/>
-      <c r="E70" s="3" t="inlineStr"/>
-      <c r="F70" s="3" t="inlineStr">
-        <is>
-          <t>ремонт/замена — минус-слова кампании; «замена платы» может быть покупкой — решить</t>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>не брать</t>
+        </is>
+      </c>
+      <c r="D70" s="6" t="inlineStr"/>
+      <c r="E70" s="6" t="inlineStr"/>
+      <c r="F70" s="6" t="inlineStr">
+        <is>
+          <t>ремонт — запрос на услугу, мы не ремонтируем</t>
         </is>
       </c>
     </row>
@@ -2372,55 +2388,63 @@
           <t>под вопросом</t>
         </is>
       </c>
-      <c r="D71" s="3" t="inlineStr"/>
-      <c r="E71" s="3" t="inlineStr"/>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t>dq200_landing.tsv</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="inlineStr">
+        <is>
+          <t>? Замена платы DQ200</t>
+        </is>
+      </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>ремонт/замена — минус-слова кампании; «замена платы» может быть покупкой — решить</t>
+          <t>замена = покупка новой платы; ставка 40 ₽</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="3" t="inlineStr">
+      <c r="A72" s="6" t="inlineStr">
         <is>
           <t>ремонт платы дсг 7 dq200</t>
         </is>
       </c>
-      <c r="B72" s="3" t="n">
+      <c r="B72" s="6" t="n">
         <v>13</v>
       </c>
-      <c r="C72" s="3" t="inlineStr">
-        <is>
-          <t>под вопросом</t>
-        </is>
-      </c>
-      <c r="D72" s="3" t="inlineStr"/>
-      <c r="E72" s="3" t="inlineStr"/>
-      <c r="F72" s="3" t="inlineStr">
-        <is>
-          <t>ремонт/замена — минус-слова кампании; «замена платы» может быть покупкой — решить</t>
+      <c r="C72" s="6" t="inlineStr">
+        <is>
+          <t>не брать</t>
+        </is>
+      </c>
+      <c r="D72" s="6" t="inlineStr"/>
+      <c r="E72" s="6" t="inlineStr"/>
+      <c r="F72" s="6" t="inlineStr">
+        <is>
+          <t>ремонт — запрос на услугу, мы не ремонтируем</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="3" t="inlineStr">
+      <c r="A73" s="6" t="inlineStr">
         <is>
           <t>ремонт платы мехатроника dsg 7 dq200 цена</t>
         </is>
       </c>
-      <c r="B73" s="3" t="n">
+      <c r="B73" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="C73" s="3" t="inlineStr">
-        <is>
-          <t>под вопросом</t>
-        </is>
-      </c>
-      <c r="D73" s="3" t="inlineStr"/>
-      <c r="E73" s="3" t="inlineStr"/>
-      <c r="F73" s="3" t="inlineStr">
-        <is>
-          <t>ремонт/замена — минус-слова кампании; «замена платы» может быть покупкой — решить</t>
+      <c r="C73" s="6" t="inlineStr">
+        <is>
+          <t>не брать</t>
+        </is>
+      </c>
+      <c r="D73" s="6" t="inlineStr"/>
+      <c r="E73" s="6" t="inlineStr"/>
+      <c r="F73" s="6" t="inlineStr">
+        <is>
+          <t>ремонт — запрос на услугу, мы не ремонтируем</t>
         </is>
       </c>
     </row>
@@ -2447,24 +2471,24 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="3" t="inlineStr">
+      <c r="A75" s="6" t="inlineStr">
         <is>
           <t>ремонт электронной платы мехатроника dsg 7</t>
         </is>
       </c>
-      <c r="B75" s="3" t="n">
+      <c r="B75" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="C75" s="3" t="inlineStr">
-        <is>
-          <t>под вопросом</t>
-        </is>
-      </c>
-      <c r="D75" s="3" t="inlineStr"/>
-      <c r="E75" s="3" t="inlineStr"/>
-      <c r="F75" s="3" t="inlineStr">
-        <is>
-          <t>ремонт/замена — минус-слова кампании; «замена платы» может быть покупкой — решить</t>
+      <c r="C75" s="6" t="inlineStr">
+        <is>
+          <t>не брать</t>
+        </is>
+      </c>
+      <c r="D75" s="6" t="inlineStr"/>
+      <c r="E75" s="6" t="inlineStr"/>
+      <c r="F75" s="6" t="inlineStr">
+        <is>
+          <t>ремонт — запрос на услугу, мы не ремонтируем</t>
         </is>
       </c>
     </row>

--- a/data/direct/wordstat_2026-10-28.xlsx
+++ b/data/direct/wordstat_2026-10-28.xlsx
@@ -3357,24 +3357,24 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="4" t="inlineStr">
+      <c r="A106" s="6" t="inlineStr">
         <is>
           <t>0am p176c</t>
         </is>
       </c>
-      <c r="B106" s="4" t="n">
+      <c r="B106" s="6" t="n">
         <v>14</v>
       </c>
-      <c r="C106" s="4" t="inlineStr">
-        <is>
-          <t>проверить</t>
-        </is>
-      </c>
-      <c r="D106" s="4" t="inlineStr"/>
-      <c r="E106" s="4" t="inlineStr"/>
-      <c r="F106" s="4" t="inlineStr">
-        <is>
-          <t>код не подтверждён источниками как мехатроник DQ200 — не беру до проверки</t>
+      <c r="C106" s="6" t="inlineStr">
+        <is>
+          <t>не брать</t>
+        </is>
+      </c>
+      <c r="D106" s="6" t="inlineStr"/>
+      <c r="E106" s="6" t="inlineStr"/>
+      <c r="F106" s="6" t="inlineStr">
+        <is>
+          <t>не подтверждено для DQ200 (выдача про DQ381/DQ500); частота 14</t>
         </is>
       </c>
     </row>
@@ -3401,24 +3401,24 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="4" t="inlineStr">
+      <c r="A108" s="6" t="inlineStr">
         <is>
           <t>р184а00 ошибка дсг7 фольксваген</t>
         </is>
       </c>
-      <c r="B108" s="4" t="n">
+      <c r="B108" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="C108" s="4" t="inlineStr">
-        <is>
-          <t>проверить</t>
-        </is>
-      </c>
-      <c r="D108" s="4" t="inlineStr"/>
-      <c r="E108" s="4" t="inlineStr"/>
-      <c r="F108" s="4" t="inlineStr">
-        <is>
-          <t>код не подтверждён источниками как мехатроник DQ200 — не беру до проверки</t>
+      <c r="C108" s="6" t="inlineStr">
+        <is>
+          <t>не брать</t>
+        </is>
+      </c>
+      <c r="D108" s="6" t="inlineStr"/>
+      <c r="E108" s="6" t="inlineStr"/>
+      <c r="F108" s="6" t="inlineStr">
+        <is>
+          <t>не подтверждено для DQ200 (выдача про DQ381/DQ500); частота 8</t>
         </is>
       </c>
     </row>
@@ -3445,46 +3445,46 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="4" t="inlineStr">
+      <c r="A110" s="6" t="inlineStr">
         <is>
           <t>ошибка 1731 дсг7</t>
         </is>
       </c>
-      <c r="B110" s="4" t="n">
+      <c r="B110" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="C110" s="4" t="inlineStr">
-        <is>
-          <t>проверить</t>
-        </is>
-      </c>
-      <c r="D110" s="4" t="inlineStr"/>
-      <c r="E110" s="4" t="inlineStr"/>
-      <c r="F110" s="4" t="inlineStr">
-        <is>
-          <t>код не подтверждён источниками как мехатроник DQ200 — не беру до проверки</t>
+      <c r="C110" s="6" t="inlineStr">
+        <is>
+          <t>не брать</t>
+        </is>
+      </c>
+      <c r="D110" s="6" t="inlineStr"/>
+      <c r="E110" s="6" t="inlineStr"/>
+      <c r="F110" s="6" t="inlineStr">
+        <is>
+          <t>P173500/1731 — датчик сцепления 1 мокрых DSG7 DQ381/DQ500 (Actronics, ABS), не DQ200</t>
         </is>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="4" t="inlineStr">
+      <c r="A111" s="6" t="inlineStr">
         <is>
           <t>p173500 ошибка dsg 0am</t>
         </is>
       </c>
-      <c r="B111" s="4" t="n">
+      <c r="B111" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="C111" s="4" t="inlineStr">
-        <is>
-          <t>проверить</t>
-        </is>
-      </c>
-      <c r="D111" s="4" t="inlineStr"/>
-      <c r="E111" s="4" t="inlineStr"/>
-      <c r="F111" s="4" t="inlineStr">
-        <is>
-          <t>код не подтверждён источниками как мехатроник DQ200 — не беру до проверки</t>
+      <c r="C111" s="6" t="inlineStr">
+        <is>
+          <t>не брать</t>
+        </is>
+      </c>
+      <c r="D111" s="6" t="inlineStr"/>
+      <c r="E111" s="6" t="inlineStr"/>
+      <c r="F111" s="6" t="inlineStr">
+        <is>
+          <t>P173500/1731 — датчик сцепления 1 мокрых DSG7 DQ381/DQ500 (Actronics, ABS), не DQ200</t>
         </is>
       </c>
     </row>
